--- a/reports/backtest_history.xlsx
+++ b/reports/backtest_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,6 +573,31 @@
           <t>数据来源</t>
         </is>
       </c>
+      <c r="AA4" s="1" t="inlineStr">
+        <is>
+          <t>标普500最低收盘跌幅(%)</t>
+        </is>
+      </c>
+      <c r="AB4" s="1" t="inlineStr">
+        <is>
+          <t>QQQ最低收盘跌幅(%)</t>
+        </is>
+      </c>
+      <c r="AC4" s="1" t="inlineStr">
+        <is>
+          <t>标普500最大收盘跌幅(%)</t>
+        </is>
+      </c>
+      <c r="AD4" s="1" t="inlineStr">
+        <is>
+          <t>QQQ最大收盘跌幅(%)</t>
+        </is>
+      </c>
+      <c r="AE4" s="1" t="inlineStr">
+        <is>
+          <t>接近事件(仅参考)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -673,6 +698,23 @@
           <t>截图</t>
         </is>
       </c>
+      <c r="AA5" t="n">
+        <v>-0.6922</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.838</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.4397</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -773,6 +815,23 @@
           <t>截图</t>
         </is>
       </c>
+      <c r="AA6" t="n">
+        <v>-1.3726</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-1.0856</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-2.9792</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-3.5883</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -873,6 +932,23 @@
           <t>截图</t>
         </is>
       </c>
+      <c r="AA7" t="n">
+        <v>-4.4069</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-6.8991</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-4.5711</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-7.3424</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -971,6 +1047,23 @@
       <c r="Z8" t="inlineStr">
         <is>
           <t>截图</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>-1.8639</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-3.0424</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-2.6021</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-4.3339</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>

--- a/reports/backtest_history.xlsx
+++ b/reports/backtest_history.xlsx
@@ -575,22 +575,22 @@
       </c>
       <c r="AA4" s="1" t="inlineStr">
         <is>
-          <t>标普500最低收盘跌幅(%)</t>
+          <t>标普500基准日口径跌幅(%)</t>
         </is>
       </c>
       <c r="AB4" s="1" t="inlineStr">
         <is>
-          <t>QQQ最低收盘跌幅(%)</t>
+          <t>QQQ基准日口径跌幅(%)</t>
         </is>
       </c>
       <c r="AC4" s="1" t="inlineStr">
         <is>
-          <t>标普500最大收盘跌幅(%)</t>
+          <t>标普500峰谷回撤(%)</t>
         </is>
       </c>
       <c r="AD4" s="1" t="inlineStr">
         <is>
-          <t>QQQ最大收盘跌幅(%)</t>
+          <t>QQQ峰谷回撤(%)</t>
         </is>
       </c>
       <c r="AE4" s="1" t="inlineStr">
